--- a/nr-update-readme/ig/StructureDefinition-SurspecialiteTransversale.xlsx
+++ b/nr-update-readme/ig/StructureDefinition-SurspecialiteTransversale.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T09:56:46+00:00</t>
+    <t>2026-07-27T09:57:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
